--- a/docs/03_tests/社員登録BBテスト.xlsx
+++ b/docs/03_tests/社員登録BBテスト.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\登録\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADB4DBE-149D-4DDB-9A20-4B5ED94A37DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52EDFF1-BC1F-414C-96AC-E08E74A19AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{EF1AC5AA-4728-4773-B3EF-119D35C7CE34}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{EF1AC5AA-4728-4773-B3EF-119D35C7CE34}"/>
   </bookViews>
   <sheets>
     <sheet name="条件" sheetId="6" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="76">
   <si>
     <t>入力欄、ドロップダウンリスト</t>
     <rPh sb="0" eb="3">
@@ -223,13 +223,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>(入力不可)</t>
-    <rPh sb="1" eb="5">
-      <t>ニュウリョクフカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>完了ボタンを押して想定される結果</t>
     <rPh sb="0" eb="2">
       <t>カンリョウ</t>
@@ -498,25 +491,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>9.氏名が50字以上の場合、入力できない</t>
-    <rPh sb="2" eb="4">
-      <t>シメイ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ジ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>イジョウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>10.電話番号が不正な値の場合(ハイフン抜き)</t>
     <rPh sb="3" eb="7">
       <t>デンワバンゴウ</t>
@@ -619,28 +593,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2-1.正常値入力後、完了ボタンを押したときの画面</t>
-    <rPh sb="4" eb="7">
-      <t>セイジョウチ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ゴ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>オ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2-2.戻るボタンを押したときの挙動</t>
     <rPh sb="4" eb="5">
       <t>モド</t>
@@ -708,6 +660,73 @@
     </rPh>
     <rPh sb="6" eb="12">
       <t>セイジョウチイジョウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>条件</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウケン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Enterテスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Confirmテスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Completeテスト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>9.氏名が50字以上の場合</t>
+    <rPh sb="2" eb="4">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>バアイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>50文字以内で入力してください</t>
+    <rPh sb="2" eb="6">
+      <t>モジイナイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1-1 ,2-1.正常値入力後、完了ボタンを押したときの画面</t>
+    <rPh sb="9" eb="12">
+      <t>セイジョウチ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ゴ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="22" eb="23">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -776,7 +795,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -800,6 +819,9 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -867,16 +889,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>632732</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>24534</xdr:rowOff>
+      <xdr:rowOff>224106</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>438154</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>547011</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>8596</xdr:rowOff>
+      <xdr:rowOff>208168</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -899,8 +921,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2498148" y="255443"/>
-          <a:ext cx="1888551" cy="2524062"/>
+          <a:off x="5268232" y="450892"/>
+          <a:ext cx="1900922" cy="2478705"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -911,16 +933,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>24195</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>832</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>604766</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>37117</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>623398</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>122301</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>541755</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>158587</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -943,8 +965,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5283489" y="464008"/>
-          <a:ext cx="1914027" cy="2437352"/>
+          <a:off x="7889123" y="263903"/>
+          <a:ext cx="1923632" cy="2389327"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -955,16 +977,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>556917</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>479543</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>100462</xdr:rowOff>
+      <xdr:rowOff>191176</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>26505</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>611345</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>43639</xdr:rowOff>
+      <xdr:rowOff>134353</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -987,8 +1009,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7788446" y="332050"/>
-          <a:ext cx="2099235" cy="2490648"/>
+          <a:off x="2466186" y="417962"/>
+          <a:ext cx="2118445" cy="2437820"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -999,16 +1021,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>255784</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>103248</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>473498</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76034</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>29300</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>159289</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>247014</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>132074</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1031,8 +1053,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10116960" y="334836"/>
-          <a:ext cx="1745752" cy="2371924"/>
+          <a:off x="2460141" y="3704605"/>
+          <a:ext cx="1760159" cy="2323898"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1087,16 +1109,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>498848</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>104401</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>607706</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>122543</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>482973</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>113878</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>591831</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>132021</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1119,8 +1141,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2471083" y="3809813"/>
-          <a:ext cx="1956361" cy="2325359"/>
+          <a:off x="10540920" y="349329"/>
+          <a:ext cx="1970768" cy="2277335"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1131,16 +1153,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>276225</xdr:colOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>13151</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>27454</xdr:rowOff>
+      <xdr:rowOff>36526</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>231775</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>630915</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>203086</xdr:rowOff>
+      <xdr:rowOff>212158</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1163,8 +1185,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4878107" y="3732866"/>
-          <a:ext cx="1927786" cy="2491514"/>
+          <a:off x="7297508" y="3665097"/>
+          <a:ext cx="1942193" cy="2443490"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1175,16 +1197,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>593725</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>197784</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>548367</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>43569</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>53788</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>119416</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>8431</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>191987</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1207,8 +1229,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8482666" y="3903196"/>
-          <a:ext cx="2089710" cy="2469102"/>
+          <a:off x="5846081" y="7073926"/>
+          <a:ext cx="2108921" cy="2416275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1219,16 +1241,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>338419</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>124758</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>274919</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>79401</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>414619</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>52740</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>351118</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>7383</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1251,8 +1273,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10857007" y="3830170"/>
-          <a:ext cx="2048436" cy="2475452"/>
+          <a:off x="8221490" y="7109758"/>
+          <a:ext cx="2062842" cy="2422625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1263,16 +1285,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>163284</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>571498</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>127001</xdr:rowOff>
+      <xdr:rowOff>18144</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>598750</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>344750</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>136070</xdr:rowOff>
+      <xdr:rowOff>27213</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1295,7 +1317,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="163284" y="6930572"/>
+          <a:off x="3220355" y="6821715"/>
           <a:ext cx="1759895" cy="2050141"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1307,16 +1329,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>628</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>68541</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>64127</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>141113</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>598715</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>31348</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>103920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1339,7 +1361,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2649485" y="6872112"/>
+          <a:off x="10659556" y="3769684"/>
           <a:ext cx="1922516" cy="2457450"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1351,16 +1373,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>383190</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>71166</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>47547</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>25808</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>254001</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>212879</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>580572</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>167522</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1383,8 +1405,52 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5018690" y="6874737"/>
+          <a:off x="47547" y="6602594"/>
           <a:ext cx="2519668" cy="3089928"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>99786</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>623255</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>199571</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63F97DD7-563E-D478-110F-157988CE8F22}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4635500" y="3728357"/>
+          <a:ext cx="1947684" cy="2367643"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2026,16 +2092,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F500D04E-A1A5-4CF2-844E-BB8CA810F919}">
-  <dimension ref="A2:B4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="10.4140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>69</v>
+      </c>
+    </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B2" s="7">
         <v>46164</v>
@@ -2043,18 +2114,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2065,7 +2136,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A47D0AA7-6BF5-4FD3-BD9F-84075E1EC2A1}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.9140625" style="2" customWidth="1"/>
@@ -2078,85 +2149,85 @@
     <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2"/>
+      <c r="D2" s="5"/>
+      <c r="F2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="2">
+      <c r="H3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2">
         <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="2">
-        <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>16</v>
@@ -2164,59 +2235,56 @@
       <c r="E5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2">
         <v>3</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="F6" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>16</v>
@@ -2227,28 +2295,25 @@
       <c r="E8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="G8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="H8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="2">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>3</v>
@@ -2257,12 +2322,12 @@
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
@@ -2270,28 +2335,28 @@
       <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>2</v>
-      </c>
       <c r="E10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="H10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>2</v>
@@ -2299,31 +2364,28 @@
       <c r="E11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="G11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="2">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="H11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="2">
-        <v>10</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="5">
-        <v>9876543210</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>3</v>
@@ -2332,12 +2394,12 @@
         <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -2345,11 +2407,11 @@
       <c r="C13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>35</v>
+      <c r="D13" s="5">
+        <v>9876543210</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>3</v>
@@ -2358,12 +2420,12 @@
         <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B14" t="s">
         <v>14</v>
@@ -2372,10 +2434,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>3</v>
@@ -2384,12 +2446,12 @@
         <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
         <v>14</v>
@@ -2398,10 +2460,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>3</v>
@@ -2410,12 +2472,12 @@
         <v>13</v>
       </c>
       <c r="H15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
         <v>14</v>
@@ -2424,24 +2486,24 @@
         <v>13</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
         <v>14</v>
@@ -2455,26 +2517,52 @@
       <c r="E17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="2">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="F3" r:id="rId1" xr:uid="{ECC8FA79-CF9C-4A96-810C-56117D7BF1E0}"/>
-    <hyperlink ref="F5" r:id="rId2" xr:uid="{53B4BAF1-9189-4FA4-95D1-46D20022D0B5}"/>
-    <hyperlink ref="F8" r:id="rId3" xr:uid="{F13D7A39-69BA-4B17-B3EC-0FF0EC83D7F3}"/>
-    <hyperlink ref="F9" r:id="rId4" xr:uid="{6E599E14-9568-42E4-B9BD-1A5F9BD5B183}"/>
-    <hyperlink ref="F17" r:id="rId5" xr:uid="{06BF53D4-9DED-46CA-86DB-902B71C7CD51}"/>
-    <hyperlink ref="F11:F14" r:id="rId6" display="a@b" xr:uid="{94A3E541-8FF5-4969-AE34-9AF85C02A647}"/>
-    <hyperlink ref="F15" r:id="rId7" xr:uid="{AE825943-13CD-4BB5-B316-147789829653}"/>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{ECC8FA79-CF9C-4A96-810C-56117D7BF1E0}"/>
+    <hyperlink ref="F6" r:id="rId2" xr:uid="{53B4BAF1-9189-4FA4-95D1-46D20022D0B5}"/>
+    <hyperlink ref="F9" r:id="rId3" xr:uid="{F13D7A39-69BA-4B17-B3EC-0FF0EC83D7F3}"/>
+    <hyperlink ref="F10" r:id="rId4" xr:uid="{6E599E14-9568-42E4-B9BD-1A5F9BD5B183}"/>
+    <hyperlink ref="F18" r:id="rId5" xr:uid="{06BF53D4-9DED-46CA-86DB-902B71C7CD51}"/>
+    <hyperlink ref="F12:F15" r:id="rId6" display="a@b" xr:uid="{94A3E541-8FF5-4969-AE34-9AF85C02A647}"/>
+    <hyperlink ref="F16" r:id="rId7" xr:uid="{AE825943-13CD-4BB5-B316-147789829653}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2482,34 +2570,39 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A60A9B8-D5B9-46CC-9151-F2CA1D28F35D}">
-  <dimension ref="A2:B4"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="5"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2520,15 +2613,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AA34D-D6E7-42B9-8EB6-421414FD2AE9}">
-  <dimension ref="A2:B3"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>72</v>
+      </c>
+    </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2">
         <v>3.1</v>
       </c>
       <c r="B2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
@@ -2536,7 +2634,7 @@
         <v>3.2</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2552,49 +2650,49 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E1" t="s">
         <v>46</v>
       </c>
       <c r="I1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="M1" t="s">
         <v>47</v>
       </c>
       <c r="Q1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
         <v>50</v>
       </c>
-      <c r="E16" t="s">
-        <v>49</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="H16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L16" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
         <v>53</v>
       </c>
-      <c r="N16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" t="s">
+      <c r="F29" t="s">
         <v>54</v>
       </c>
-      <c r="I30" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="N31" t="s">
-        <v>52</v>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J30" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.55000000000000004">
@@ -2624,10 +2722,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="J2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
@@ -2640,10 +2738,10 @@
         <v>2</v>
       </c>
       <c r="J15" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="O15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">

--- a/docs/03_tests/社員登録BBテスト.xlsx
+++ b/docs/03_tests/社員登録BBテスト.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fullness\Downloads\登録\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D52EDFF1-BC1F-414C-96AC-E08E74A19AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AE740A4-8520-4D0D-8A4F-89D6D50C875A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="5" xr2:uid="{EF1AC5AA-4728-4773-B3EF-119D35C7CE34}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="Enterテスト" sheetId="3" r:id="rId2"/>
     <sheet name="Confirmテスト" sheetId="4" r:id="rId3"/>
     <sheet name="Completeテスト" sheetId="5" r:id="rId4"/>
-    <sheet name="異常系" sheetId="1" r:id="rId5"/>
-    <sheet name="正常系" sheetId="2" r:id="rId6"/>
+    <sheet name="正常系" sheetId="2" r:id="rId5"/>
+    <sheet name="異常系" sheetId="1" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="83">
   <si>
     <t>入力欄、ドロップダウンリスト</t>
     <rPh sb="0" eb="3">
@@ -727,6 +727,46 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リロードをしたとき、Enterページに戻る</t>
+    <rPh sb="19" eb="20">
+      <t>モド</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3-3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>リロードをする値を保持したままConfirmページに</t>
+    <rPh sb="7" eb="8">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2-4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>続行をクリック</t>
+    <rPh sb="0" eb="2">
+      <t>ゾッコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -795,7 +835,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -823,6 +863,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -842,6 +885,555 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>114445</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>26296</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>648409</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>112530</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{683892E0-04F9-4084-B100-B2D4DD9BD327}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="114445" y="706653"/>
+          <a:ext cx="1858393" cy="2354091"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>52627</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>173324</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>117795</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>213326</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BCAAE3C-AC55-43E6-9A9B-75B22C1D5464}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2701484" y="626895"/>
+          <a:ext cx="2714025" cy="1627502"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>182637</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>120476</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>10050</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>164381</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6748BDB7-485F-48A3-BFB5-CF24EA647607}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6142566" y="574047"/>
+          <a:ext cx="1814055" cy="2311763"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>314428</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>123642</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>263699</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>35532</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3439245-AB97-4087-A611-CAFB9919FB28}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5612142" y="3525428"/>
+          <a:ext cx="2598128" cy="2179747"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>387447</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>7225</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>39311</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>54429</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98B64F49-24B9-4EBB-8712-5F5F0810B5AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8996233" y="3862582"/>
+          <a:ext cx="2962935" cy="954347"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>126999</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>623169</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>181428</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D475A4A-B714-1385-72CA-217C54C30811}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8799286" y="353785"/>
+          <a:ext cx="3081526" cy="1415143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>277737</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>48217</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>373743</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>132989</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{325699E0-D6CC-51F1-13A9-6F917B85F721}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4251023" y="6171431"/>
+          <a:ext cx="2082649" cy="2352629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>399143</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>399144</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1815</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B21577A-FB6F-1C69-515D-716DE504E506}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="399143" y="6123214"/>
+          <a:ext cx="2648858" cy="1589315"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>408215</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>154216</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>317501</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>35340</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32D82A01-0B85-C659-3868-2DFFB07DB20A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="408215" y="8545287"/>
+          <a:ext cx="3220357" cy="1695410"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>290285</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>117929</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>653142</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>81643</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="矢印: 下 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33EADF97-8DB9-5B9A-964E-16742DEF5B1E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1614714" y="7828643"/>
+          <a:ext cx="362857" cy="644071"/>
+        </a:xfrm>
+        <a:prstGeom prst="downArrow">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>362857</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>117928</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>489857</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>219227</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A941F42-0484-988D-BD65-AED95C01E8C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10958286" y="6241142"/>
+          <a:ext cx="2113642" cy="2142371"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>462643</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>72572</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>96646</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>217715</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57DA4F6B-A30C-423C-FA1D-501440D286E6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7084786" y="6195786"/>
+          <a:ext cx="2945074" cy="1732643"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1462,319 +2054,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>114445</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>26296</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>648409</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>112530</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{683892E0-04F9-4084-B100-B2D4DD9BD327}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="114445" y="706653"/>
-          <a:ext cx="1858393" cy="2354091"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>52627</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>173324</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>117795</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>213326</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0BCAAE3C-AC55-43E6-9A9B-75B22C1D5464}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2701484" y="626895"/>
-          <a:ext cx="2714025" cy="1627502"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>182637</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>120476</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>10050</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>164381</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6748BDB7-485F-48A3-BFB5-CF24EA647607}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6142566" y="574047"/>
-          <a:ext cx="1814055" cy="2311763"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>314428</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>123642</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>263699</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>35532</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3439245-AB97-4087-A611-CAFB9919FB28}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5612142" y="3525428"/>
-          <a:ext cx="2598128" cy="2179747"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>387447</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>7225</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>39311</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>54429</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98B64F49-24B9-4EBB-8712-5F5F0810B5AB}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8996233" y="3862582"/>
-          <a:ext cx="2962935" cy="954347"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>126999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>623169</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>181428</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D475A4A-B714-1385-72CA-217C54C30811}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8799286" y="353785"/>
-          <a:ext cx="3081526" cy="1415143"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>132594</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>11931</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>96703</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{325699E0-D6CC-51F1-13A9-6F917B85F721}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="132594" y="6184131"/>
-          <a:ext cx="2077206" cy="2370772"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -2570,6 +2849,57 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A60A9B8-D5B9-46CC-9151-F2CA1D28F35D}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="5" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AA34D-D6E7-42B9-8EB6-421414FD2AE9}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -2578,63 +2908,31 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="5" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AA34D-D6E7-42B9-8EB6-421414FD2AE9}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>3.1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
-        <v>3.2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -2644,124 +2942,72 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDBF789-A04D-428E-A690-1E498D85B924}">
-  <dimension ref="A1:Q45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FCE7A5F-1E2C-435A-AD31-C385657C5256}">
+  <dimension ref="A2:Q36"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E1" t="s">
-        <v>46</v>
-      </c>
-      <c r="I1" t="s">
-        <v>45</v>
-      </c>
-      <c r="M1" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16" t="s">
-        <v>49</v>
-      </c>
-      <c r="E16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H16" t="s">
-        <v>73</v>
-      </c>
-      <c r="L16" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>53</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="J30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" t="s">
-        <v>6</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FCE7A5F-1E2C-435A-AD31-C385657C5256}">
-  <dimension ref="A2:O26"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="16384" width="8.6640625" style="5"/>
+  </cols>
   <sheetData>
     <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="5" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="E14" t="s">
+      <c r="E14" s="5" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="E15" t="s">
+      <c r="E15" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="O15" t="s">
+      <c r="O15" s="5" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E17" t="s">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="E19" t="s">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="E19" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>3.1</v>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="D36" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2772,4 +3018,73 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEDBF789-A04D-428E-A690-1E498D85B924}">
+  <dimension ref="A1:Q45"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" t="s">
+        <v>73</v>
+      </c>
+      <c r="L16" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F29" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="J30" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>